--- a/gosi/output/시군구_공보게시판_목록_new.xlsx
+++ b/gosi/output/시군구_공보게시판_목록_new.xlsx
@@ -8727,7 +8727,7 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>후보만(수동확인 필요)</t>
+          <t>제외(사용자 지시 2026-10-31)</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>e-book/JS 화면 가능</t>
+          <t>경기도보: 양이 너무 많아 수집하지 않음</t>
         </is>
       </c>
       <c r="L112" s="12" t="n"/>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="F182" s="10" t="inlineStr">
         <is>
-          <t>후보만(수동확인 필요)</t>
+          <t>제외(사용자 지시 2026-10-31)</t>
         </is>
       </c>
       <c r="G182" s="10" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="K182" s="10" t="inlineStr">
         <is>
-          <t>e-book/JS 화면 가능</t>
+          <t>서귀포시: 시보·공보를 찾을 수 없음(제주도 도보로 대체)</t>
         </is>
       </c>
       <c r="L182" s="12" t="n"/>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="F183" s="10" t="inlineStr">
         <is>
-          <t>후보만(수동확인 필요)</t>
+          <t>제외(사용자 지시 2026-10-31)</t>
         </is>
       </c>
       <c r="G183" s="10" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="K183" s="10" t="inlineStr">
         <is>
-          <t>e-book/JS 화면 가능</t>
+          <t>제주시: 시보·공보를 찾을 수 없음(제주도 도보로 대체)</t>
         </is>
       </c>
       <c r="L183" s="12" t="n"/>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F189" s="10" t="inlineStr">
         <is>
-          <t>후보만(수동확인 필요)</t>
+          <t>제외(사용자 지시 2026-10-31)</t>
         </is>
       </c>
       <c r="G189" s="10" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="K189" s="10" t="inlineStr">
         <is>
-          <t>e-book/JS 화면 가능</t>
+          <t>서산시: 공보 없음(서산소식지·시정백서뿐)·제외</t>
         </is>
       </c>
       <c r="L189" s="12" t="n"/>
